--- a/data/trans_bre/IQ2608_R3-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IQ2608_R3-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21,63</t>
+          <t>18,91</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>35,03%</t>
+          <t>32,97%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-14,03; 8,26</t>
+          <t>-14,87; 8,43</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-9,46; 10,27</t>
+          <t>-9,05; 10,03</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-15,0; 5,76</t>
+          <t>-14,52; 6,23</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-9,24; 51,68</t>
+          <t>-15,4; 50,22</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-18,36; 12,49</t>
+          <t>-19,72; 13,21</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-10,96; 13,37</t>
+          <t>-10,41; 13,19</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-16,48; 6,86</t>
+          <t>-16,12; 7,19</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-12,62; 138,39</t>
+          <t>-21,39; 140,25</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-6,81</t>
+          <t>-6,47</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-9,83%</t>
+          <t>-9,45%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,21; 4,43</t>
+          <t>-6,01; 4,53</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,48; 3,13</t>
+          <t>-5,55; 2,66</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-7,22; 1,16</t>
+          <t>-7,2; 0,92</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-17,65; 4,44</t>
+          <t>-17,44; 5,67</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-9,91; 7,7</t>
+          <t>-9,63; 7,89</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-6,68; 3,99</t>
+          <t>-6,64; 3,39</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-8,45; 1,42</t>
+          <t>-8,53; 1,14</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-24,48; 7,14</t>
+          <t>-23,95; 8,57</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-5,0</t>
+          <t>-6,09</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-7,04%</t>
+          <t>-8,53%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-16,8; 0,65</t>
+          <t>-16,49; 0,55</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,77; 5,47</t>
+          <t>-7,32; 5,58</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,27; 5,06</t>
+          <t>-8,7; 5,05</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-20,49; 12,0</t>
+          <t>-22,99; 11,37</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-23,43; 1,38</t>
+          <t>-22,71; 0,96</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-8,75; 6,58</t>
+          <t>-8,19; 6,74</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-9,58; 6,48</t>
+          <t>-10,16; 6,34</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-26,08; 19,11</t>
+          <t>-29,16; 18,17</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-3,95</t>
+          <t>-4,52</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-5,72%</t>
+          <t>-6,6%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-7,5; 0,84</t>
+          <t>-7,01; 1,2</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,13; 2,55</t>
+          <t>-4,32; 2,24</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-6,05; 0,6</t>
+          <t>-6,31; 0,31</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-13,41; 4,82</t>
+          <t>-13,67; 5,01</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-11,38; 1,35</t>
+          <t>-10,79; 1,95</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-4,95; 3,24</t>
+          <t>-5,17; 2,74</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-7,15; 0,68</t>
+          <t>-7,37; 0,37</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-18,84; 7,66</t>
+          <t>-18,85; 7,91</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IQ2608_R3-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IQ2608_R3-Estudios-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,199 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-4,18</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0,28</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-4,01</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>18,91</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-5,84%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-4,6%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>32,97%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>-4.182464631795946</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.2782521052361209</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-4.005480659630223</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>18.91059038613442</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>-0.05844197638727124</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>0.003434437942380667</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>-0.04604247221607594</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>0.3297262808373209</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-14,87; 8,43</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-9,05; 10,03</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-14,52; 6,23</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-15,4; 50,22</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-19,72; 13,21</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-10,41; 13,19</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-16,12; 7,19</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-21,39; 140,25</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-14.87499984859998</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-9.054066498934938</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-14.52014338222445</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-15.40370183475391</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.1971550097451817</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.1041006633320369</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-0.1612250427445404</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>-0.2138897906834161</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>8.426181630361182</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>10.03260282739872</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>6.228042252010193</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>50.22490961078064</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0.1321301907674819</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>0.1319462156589938</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>0.07194181689622289</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>1.402460358216642</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Secundarios</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-1,01</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-1,3</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-2,99</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-6,47</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-1,67%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-1,62%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-3,59%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-9,45%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-6,01; 4,53</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-5,55; 2,66</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-7,2; 0,92</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-17,44; 5,67</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-9,63; 7,89</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-6,64; 3,39</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-8,53; 1,14</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-23,95; 8,57</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-1.011050094159649</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-1.302322840828041</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-2.987283523997042</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-6.465005682041824</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.01665261964390105</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.01618461216511818</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>-0.03588789212679462</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-0.09447862393383626</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-8,54</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-0,91</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-1,49</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-6,09</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-12,62%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-1,05%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-1,82%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-8,53%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-6.010113725288768</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-5.545912550992012</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-7.199851632111648</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-17.43629164612654</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.09632977801505485</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.06639405897321866</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.08527546949832863</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.2394785525550573</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-16,49; 0,55</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-7,32; 5,58</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-8,7; 5,05</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-22,99; 11,37</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-22,71; 0,96</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-8,19; 6,74</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-10,16; 6,34</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-29,16; 18,17</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>4.525670689849066</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>2.662231185032002</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.9222970171631971</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>5.672998988640025</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.07894288573983493</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.03385989476936661</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>0.0113821596061315</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>0.08572488221363275</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Universitarios</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,97 +819,197 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-2,94</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-0,96</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-2,74</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-4,52</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-4,62%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-1,17%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-3,29%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-6,6%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-8.540334915260772</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-0.9086778224504433</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-1.493497146084544</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-6.088549482810246</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.1262163909604004</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-0.01054231129766377</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>-0.01824656827246853</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>-0.0852816797786165</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-7,01; 1,2</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-4,32; 2,24</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-6,31; 0,31</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-13,67; 5,01</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-10,79; 1,95</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-5,17; 2,74</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-7,37; 0,37</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-18,85; 7,91</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-16.4886717803658</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-7.322412705821763</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-8.699377928352447</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-22.99107837564235</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.2270776208375971</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.08188525478893596</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.1016364593892428</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.2915746571348659</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.5523114781273288</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>5.576959729936309</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>5.050702509822607</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>11.36949384735248</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.009595213832170544</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>0.06739902461340165</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>0.06336744699329919</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>0.1816917558448676</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>-2.935485427841689</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-0.9574753985674422</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-2.735871521137989</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-4.515526901115996</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.04621455945892558</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.01170194028924411</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>-0.03286502019176372</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-0.06604070738185348</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-7.014913550629132</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-4.319533199064731</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-6.305370556775001</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-13.66710817466211</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.1078666037980425</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.05166470229491499</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.07373131052137642</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.188474352558203</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>1.196638151099519</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>2.24433829524551</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.3104098169418997</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>5.008386819733057</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.01952122308644873</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.02741781260941125</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>0.003651554403977374</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>0.07910177876466264</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1008,13 +1017,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
